--- a/sources/igaming-daily-report-sources-v2.xlsx
+++ b/sources/igaming-daily-report-sources-v2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料來源清單" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="資料來源清單" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E234"/>
+  <dimension ref="A1:H242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -558,6 +558,21 @@
           <t>備註</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>抓取方式</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>抓取端點</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr"/>
@@ -586,6 +601,21 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://pragmaticplay.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -611,6 +641,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -636,6 +677,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -661,6 +713,21 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.playngo.com/blog-feed.xml</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -686,6 +753,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -711,6 +789,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -736,6 +825,17 @@
           <t>Provider 官網（Crash 代表廠商）</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -761,6 +861,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -786,6 +897,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -811,6 +933,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -836,6 +969,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -861,6 +1005,21 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.thunderkick.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -886,6 +1045,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -911,6 +1081,17 @@
           <t>Provider 官網；⭐優先展示品牌</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -936,6 +1117,21 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://betsoft.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -961,6 +1157,21 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://fantasmagames.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -986,6 +1197,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1011,6 +1233,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1036,6 +1269,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1061,6 +1305,21 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://4theplayer.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1086,6 +1345,21 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://avatarux.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1111,6 +1385,21 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://kalambagames.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1136,6 +1425,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1161,6 +1461,17 @@
           <t>Provider 官網</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr"/>
@@ -1189,6 +1500,21 @@
           <t>bonus hit rate、variance、max multiplier 統計</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://clashofslots.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -1214,6 +1540,17 @@
           <t>全站新遊戲上線清單</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -1239,6 +1576,17 @@
           <t>Jili 新遊戲、RTP、volatility 數據</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -1264,6 +1612,17 @@
           <t>PG Soft 新遊戲、機制數據</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -1289,6 +1648,17 @@
           <t>PP 新遊戲、機制數據，含待發布排程</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -1314,6 +1684,17 @@
           <t>遊戲機制解析、Provider 評測、玩家投訴資料庫</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -1339,6 +1720,17 @@
           <t>Slot variance 分析、Provider 評論</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -1364,6 +1756,21 @@
           <t>Provider 新聞角度的評測與分析</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.igamingtoday.com/</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -1389,6 +1796,21 @@
           <t>B2B 視角 Provider 評測，關注營運整合</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.gamingsoft.com/blog/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
@@ -1414,6 +1836,21 @@
           <t>Slot 遊戲設計分析，設計師視角拆解玩法機制</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://ezslotdesign.com/rss/</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -1439,6 +1876,17 @@
           <t>日本遊技機資料庫；子頁 introduce_calendar.cgi 為★新台上市日期／規格／導入店數，日本機種情報最關鍵單一來源</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr"/>
@@ -1467,6 +1915,21 @@
           <t>東南亞 iGaming 專業媒體，Jili 報導最完整</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://agbrief.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -1492,6 +1955,21 @@
           <t>Provider 合作、盤口動向、市場數據</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://igamingbusiness.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -1517,6 +1995,21 @@
           <t>Provider 新遊戲、合作消息</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://casinobeats.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -1542,6 +2035,21 @@
           <t>盤口動態、Provider 合作</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://sbcnews.co.uk/</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -1567,6 +2075,21 @@
           <t>盤口市場數據、M&amp;A、財務動態</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://gamblinginsider.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -1592,6 +2115,21 @@
           <t>全球市場動態、M&amp;A（每日主力來源之一）</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.yogonet.com/international/rss.xml</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -1617,6 +2155,21 @@
           <t>盤口排名、Provider 表現</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.egr.global/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -1642,6 +2195,21 @@
           <t>Provider 市場佔比 power ranking</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.businessofigaming.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -1667,6 +2235,21 @@
           <t>Provider 動態新聞</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://igamingexpert.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -1692,6 +2275,17 @@
           <t>Slot 分類快訊</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -1717,6 +2311,17 @@
           <t>按 Provider 分類的新聞彙整</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -1742,6 +2347,21 @@
           <t>美國博彩媒體，含 Provider 與市場報導</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://cdcgaming.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -1767,6 +2387,17 @@
           <t>業內分析，含 Provider 產品設計深度文章</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -1792,6 +2423,17 @@
           <t>現金網官方公告，需瀏覽器模式抓取</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -1817,6 +2459,21 @@
           <t>Slot／Provider 產品線報導；iGaming Business 子版</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://igamingbusiness.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -1842,6 +2499,21 @@
           <t>iGaming Business 深度專刊庫</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://igamingbusiness.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -1867,6 +2539,21 @@
           <t>SBC News 北美／LatAm 版</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://sbcamericas.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -1892,6 +2579,21 @@
           <t>EGR Global 深度分析／高階訪談</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.egr.global/intel/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -1917,6 +2619,21 @@
           <t>高階產業情報媒體</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.gamingintelligence.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -1942,6 +2659,17 @@
           <t>B2B／供應商動態</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -1967,6 +2695,17 @@
           <t>Online＋Land-based 綜合報導</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -1992,6 +2731,17 @@
           <t>線上 Slot 新品發表（與 cat1 高度對應）</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -2017,6 +2767,17 @@
           <t>實體機台／Cabinet 新品發表</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -2042,6 +2803,21 @@
           <t>全球供應商／機台新聞，含 Aristocrat、L&amp;W、IGT 等新品；子頁 g3newswire.com/magazines/ 為深度雜誌</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://g3newswire.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
@@ -2067,6 +2843,17 @@
           <t>北美實體 Slot／Casino Floor；子頁 /publications/ 與 /publications/ggb-magazine/ 為專刊庫</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -2092,6 +2879,21 @@
           <t>Provider 新遊戲更新速度快；另有地區版 Africa／Asia Pacific／Brasil／Latinoamérica（見下列各行）</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://focusgn.com/feed</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
@@ -2117,6 +2919,21 @@
           <t>Slot、game development 專題</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://gaminginternational.online/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -2142,6 +2959,21 @@
           <t>實體 Slot／Supplier 報導</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://casinointernational-online.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
@@ -2167,6 +2999,21 @@
           <t>Casino／Supplier 產業雜誌</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.casinolifemagazine.com/rss.xml</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -2192,6 +3039,21 @@
           <t>Casino Technology 報導</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://mygamingandleisure.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
@@ -2217,6 +3079,21 @@
           <t>北美 Tribal Casino；子頁 /magazine/ 為雜誌版</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.indiangaming.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
@@ -2242,6 +3119,21 @@
           <t>Technology／Product 報導；子頁 /category/casino/ 為 Casino／Slot 專區（優先級較高）</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://igamingfuture.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
@@ -2267,6 +3159,21 @@
           <t>B2B／訪談；子頁 /news/ 為 Supplier／Product 新聞</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://igamingenquirer.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
@@ -2292,6 +3199,21 @@
           <t>Slot Launch 報導</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.timesofcasino.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
@@ -2317,6 +3239,17 @@
           <t>Casino Guru 新聞版（與已收錄的 Casino Guru 評測庫互補）</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
@@ -2342,6 +3275,17 @@
           <t>Provider 高階主管長訪，格式獨特</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
@@ -2367,6 +3311,21 @@
           <t>北美 iGaming 報導；子頁 /news/ 為新聞版</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.casinoreports.com/rss.xml</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
@@ -2392,6 +3351,21 @@
           <t>加拿大 Online Casino 專版</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.casinoreports.ca/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
@@ -2417,6 +3391,21 @@
           <t>歐洲 B2B 產業媒體</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://europeangaming.eu/portal/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
@@ -2442,6 +3431,17 @@
           <t>SiGMA 新聞版（既有清單僅收錄展會頁）；另有繁中／俄語版</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
@@ -2467,6 +3467,17 @@
           <t>Yogonet 拉美版</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
@@ -2492,6 +3503,17 @@
           <t>Yogonet 巴西版（PT-BR）</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
@@ -2517,6 +3539,21 @@
           <t>西語／英語拉美博彩媒體</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://soloazar.com/es/feed</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
@@ -2542,6 +3579,21 @@
           <t>LatAm Provider、Game launch 報導</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://zonadeazar.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
@@ -2567,6 +3619,17 @@
           <t>西語博彩媒體</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
@@ -2592,6 +3655,21 @@
           <t>西語博彩媒體</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.azarplus.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
@@ -2617,6 +3695,21 @@
           <t>西語博彩產業媒體</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://sectordeljuego.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
@@ -2642,6 +3735,17 @@
           <t>西語 Land-based 報導</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
@@ -2667,6 +3771,21 @@
           <t>秘魯／拉美博彩雜誌</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.revistacasinoperu.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
@@ -2692,6 +3811,21 @@
           <t>哥倫比亞博彩雜誌</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://apuestacolombia.com.co/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
@@ -2717,6 +3851,21 @@
           <t>SBC News 西語版；子頁 /br/ 為巴西葡語版</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://sbcnoticias.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
@@ -2742,6 +3891,21 @@
           <t>SBC News 巴西葡語版</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://sbcnoticias.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
@@ -2767,6 +3931,21 @@
           <t>巴西 iGaming 專業媒體</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://igamingbrazil.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
@@ -2792,6 +3971,17 @@
           <t>巴西遊戲產業雜誌</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
@@ -2817,6 +4007,21 @@
           <t>義大利博彩媒體</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://www.gioconews.it/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
@@ -2842,6 +4047,21 @@
           <t>義大利博彩媒體</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.agimeg.it/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
@@ -2867,6 +4087,21 @@
           <t>義大利 Slot、Provider 排名；子頁 /slot-e-vlt/ 為 Slot／VLT 專區</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://www.agipronews.it/rss</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
@@ -2892,6 +4127,21 @@
           <t>義大利博彩媒體</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://www.pressgiochi.it/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
@@ -2917,6 +4167,21 @@
           <t>英語歐洲研究型季刊</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://www.ogqnews.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
@@ -2942,6 +4207,21 @@
           <t>德國實體 Gaming 媒體</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.automatenmarkt.de/rss</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
@@ -2967,6 +4247,21 @@
           <t>★德國新機／Field Test 專區，最具追蹤價值</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.automatenmarkt.de/rss</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
@@ -2992,6 +4287,21 @@
           <t>德國 B2B 媒體</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://www.gamesundbusiness.de/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
@@ -3017,6 +4327,21 @@
           <t>德語 Casino 媒體</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://www.isa-guide.de/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
@@ -3042,6 +4367,17 @@
           <t>法國 Casino B2B 媒體</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
@@ -3067,6 +4403,21 @@
           <t>法國 Casino 媒體</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>http://www.lescasinos.org/rss/flux.xml</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
@@ -3092,6 +4443,17 @@
           <t>荷蘭博彩媒體</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
@@ -3117,6 +4479,17 @@
           <t>荷蘭／英語博彩媒體</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
@@ -3142,6 +4515,17 @@
           <t>英／俄／烏語博彩媒體</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
@@ -3167,6 +4551,21 @@
           <t>羅馬尼亞博彩媒體</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://casinoinside.ro/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
@@ -3192,6 +4591,17 @@
           <t>羅馬尼亞／中東歐博彩媒體</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
@@ -3217,6 +4627,21 @@
           <t>波蘭博彩媒體</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://interplay.pl/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
@@ -3242,6 +4667,21 @@
           <t>日本 Pachislot 媒體；子頁 /category/machine/ 為新台專區（優先級最高）</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://web-greenbelt.jp/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
@@ -3267,6 +4707,17 @@
           <t>日本業界月刊</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
@@ -3292,6 +4743,17 @@
           <t>Pachinko／Slot 綜合媒體；子頁 /pachinko-pachislot-kentei/ 為新機審查／型號資訊</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
@@ -3317,6 +4779,17 @@
           <t>日本產業媒體</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
@@ -3342,6 +4815,21 @@
           <t>日本 B2B 媒體</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://www.yugitsushin.jp/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
@@ -3367,6 +4855,17 @@
           <t>日本機種／玩法媒體</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
@@ -3392,6 +4891,17 @@
           <t>日本 Hall／新機資訊</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
@@ -3417,6 +4927,17 @@
           <t>日本遊技專門誌</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
@@ -3442,6 +4963,17 @@
           <t>日本業界情報入口網</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
@@ -3467,6 +4999,21 @@
           <t>澳門／亞洲 Casino floor 報導</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://www.ggrasia.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
@@ -3492,6 +5039,21 @@
           <t>亞洲供應商、機台、展會報導</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://www.asgam.com/</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
@@ -3517,6 +5079,21 @@
           <t>AGB 澳門專版</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://agbrief.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
@@ -3542,6 +5119,21 @@
           <t>★AGB 菲律賓專版，直接對應本報告 🇵🇭 分類</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://agbrief.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
@@ -3567,6 +5159,21 @@
           <t>AGB 越南專版</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://agbrief.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
@@ -3592,6 +5199,17 @@
           <t>澳門商業／博彩媒體（EN／PT）</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
@@ -3617,6 +5235,17 @@
           <t>澳門日報英文版</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
@@ -3642,6 +5271,21 @@
           <t>非洲 B2B 媒體</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://igamingafrika.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
@@ -3667,6 +5311,21 @@
           <t>非洲市場分析子站</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://insight.ageafrique.org/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
@@ -3692,6 +5351,17 @@
           <t>非洲 B2B 雜誌</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
@@ -3717,6 +5387,21 @@
           <t>非洲博彩媒體；子頁含東非專版</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://findmoreafrica.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
@@ -3742,6 +5427,21 @@
           <t>Focus Gaming News 非洲版</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://focusgn.com/feed</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
@@ -3767,6 +5467,21 @@
           <t>★Focus Gaming News 亞太版，對應本報告亞洲焦點</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://focusgn.com/feed</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
@@ -3792,6 +5507,21 @@
           <t>Focus Gaming News 巴西版</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://focusgn.com/feed</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
@@ -3817,6 +5547,21 @@
           <t>Focus Gaming News 拉美西語版</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://focusgn.com/feed</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr"/>
@@ -3845,6 +5590,17 @@
           <t>玩家討論 slot 遊戲體驗、Provider 產品反應</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
@@ -3870,6 +5626,17 @@
           <t>廣泛討論 Provider 與盤口體驗</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
@@ -3895,6 +5662,17 @@
           <t>玩家＋業內討論，含 Provider 投訴與產品反應</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
@@ -3920,6 +5698,17 @@
           <t>專屬 Game Provider 討論板，含促銷與新聞</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
@@ -3945,6 +5734,17 @@
           <t>Slot 玩家論壇</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
@@ -3970,6 +5770,17 @@
           <t>老牌業界論壇，玩家＋業內人士混合</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="9" t="inlineStr"/>
@@ -3998,6 +5809,17 @@
           <t>每年 1 月，全球最大 iGaming 展，有 content hub</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
@@ -4023,6 +5845,17 @@
           <t>多地區（Malta、Manila、Rome 等）</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
@@ -4048,6 +5881,17 @@
           <t>每年秋季，北美最大；⚠️官方新網域為 globalgamingexpo.com，建議之後更新</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
@@ -4073,6 +5917,17 @@
           <t>東南亞；2026 停辦，2027 回歸 Manila</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
@@ -4098,6 +5953,17 @@
           <t>追蹤亞洲 Provider 得獎動態</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
@@ -4123,6 +5989,21 @@
           <t>展會資訊彙整，含 slot 設計視角</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://ezslotdesign.com/rss/</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
@@ -4148,6 +6029,17 @@
           <t>亞洲 Gaming 實體展會</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
@@ -4173,6 +6065,17 @@
           <t>ICE 展會 Casino／Slot 產業別頁面</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
@@ -4198,6 +6101,17 @@
           <t>ICE 展商新品發表庫</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
@@ -4223,6 +6137,17 @@
           <t>亞洲實體 Casino／Slot 展會；子頁 en-gb/media/press-release.html 為新聞稿</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
@@ -4248,6 +6173,17 @@
           <t>SiGMA 亞洲分區峰會（含菲律賓 Manila）；另有繁中版</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
@@ -4273,6 +6209,21 @@
           <t>西語／英語拉美展會</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://gatexpo.net/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
@@ -4298,6 +6249,21 @@
           <t>秘魯博彩展會</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://www.perugamingshow.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
@@ -4323,6 +6289,17 @@
           <t>拉美大型博彩展會</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
@@ -4348,6 +6325,21 @@
           <t>澳洲實體機台展會</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://austgamingexpo.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
@@ -4373,6 +6365,17 @@
           <t>非洲博彩峰會</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
@@ -4398,6 +6401,21 @@
           <t>非洲實體展會；子頁 /media/ 為報告／簡報下載庫</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://www.ageafrique.org/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
@@ -4423,6 +6441,17 @@
           <t>SiGMA 非洲分區峰會</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
@@ -4448,6 +6477,17 @@
           <t>SiGMA 南美分區峰會</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="10" t="inlineStr"/>
@@ -4476,6 +6516,17 @@
           <t>大量 slot 試玩，觀察 bonus 觸發與遊戲行為</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
@@ -4501,6 +6552,17 @@
           <t>B2B 產業訪談、Provider 趨勢分析</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
@@ -4526,6 +6588,21 @@
           <t>市場分析，含 Provider 動態</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://igamingbusiness.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
@@ -4551,6 +6628,17 @@
           <t>業內領袖訪談，聚焦 iGaming 產業策略</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
@@ -4576,6 +6664,17 @@
           <t>產業趨勢與新聞分析</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr"/>
@@ -4604,6 +6703,17 @@
           <t>西班牙官方博彩監理機關（DGOJ）研究與統計</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
@@ -4629,6 +6739,17 @@
           <t>義大利官方博彩監理機關（海關暨壟斷署）</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
@@ -4654,6 +6775,21 @@
           <t>法國官方博彩監理機關（Autorité Nationale des Jeux）</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://anj.fr/rss.xml</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
@@ -4679,6 +6815,21 @@
           <t>荷蘭官方博彩監理機關</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://kansspelautoriteit.nl/feed/rss/nieuws</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
@@ -4704,6 +6855,17 @@
           <t>比利時官方博彩監理機關</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
@@ -4729,6 +6891,17 @@
           <t>瑞士聯邦博彩監理機關</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
@@ -4754,6 +6927,17 @@
           <t>澳門官方博彩監察協調局</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
@@ -4779,6 +6963,17 @@
           <t>★菲律賓官方監理機關新聞稿，直接對應本報告 🇵🇭 分類</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
@@ -4804,6 +6999,17 @@
           <t>PAGCOR 年度報告，官方統計數據</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n">
@@ -4829,6 +7035,17 @@
           <t>哥倫比亞官方博彩監理機關新聞室</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
@@ -4854,6 +7071,17 @@
           <t>秘魯外貿旅遊部（主管賭場）官方頁</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n">
@@ -4879,6 +7107,17 @@
           <t>紐南威爾斯州政府博彩研究報告</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n">
@@ -4904,6 +7143,17 @@
           <t>紐南威爾斯州官方博彩監理機關</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n">
@@ -4929,6 +7179,17 @@
           <t>維多利亞州官方博彩監理機關</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="n">
@@ -4954,6 +7215,17 @@
           <t>昆士蘭州官方博彩監理機關</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n">
@@ -4979,6 +7251,17 @@
           <t>紐西蘭官方博彩監理機關</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="12" t="inlineStr"/>
@@ -5007,6 +7290,17 @@
           <t>★EKG 官方新網域（原 ekg.com 已停站，見既有清單「已停用」項）；子頁 /reports 為報告庫、/services/game-performance-analytics 為單款 Slot／Cabinet 真實績效服務</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n">
@@ -5032,6 +7326,17 @@
           <t>涵蓋 EMEA／LatAm／歐洲線上／美國線上／加拿大線上等區域月度 Slot／Cabinet 排名報告，逐月更新，請至 reports 頁查最新版而非收錄單一 PDF 連結</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="n">
@@ -5057,6 +7362,17 @@
           <t>美國內華達大學拉斯維加斯分校博彩學術期刊，Slot 玩家與機率研究</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="n">
@@ -5082,6 +7398,21 @@
           <t>UNLV Gaming Statistics 圖表化摘要</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://oasis.library.unlv.edu/recent.rss</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n">
@@ -5107,6 +7438,17 @@
           <t>全球博彩市場數據庫，付費情報服務</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n">
@@ -5132,6 +7474,17 @@
           <t>Market Intelligence／法規情報服務</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n">
@@ -5157,6 +7510,17 @@
           <t>博彩產業策略顧問／情報</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n">
@@ -5182,6 +7546,17 @@
           <t>Casino 產業顧問公司</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n">
@@ -5207,6 +7582,17 @@
           <t>Slot Floor Analytics，實體機台效能分析</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n">
@@ -5232,6 +7618,17 @@
           <t>Casino Floor Analytics</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n">
@@ -5257,6 +7654,17 @@
           <t>AI／Slot Operations 分析服務</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n">
@@ -5282,6 +7690,21 @@
           <t>Online Market Data 分析平台</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://blask.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n">
@@ -5307,6 +7730,21 @@
           <t>SOFTSWISS 年度趨勢報告微站</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://www.softswiss.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="3" t="n">
@@ -5332,6 +7770,17 @@
           <t>澳洲政府資助博彩學術研究計畫</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n">
@@ -5357,6 +7806,17 @@
           <t>澳洲家庭研究院博彩研究中心</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n">
@@ -5382,6 +7842,21 @@
           <t>巴西／拉美 Slot 市場數據；子頁 /category/slot/ 為 Slot 專區</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://bnldata.com.br/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n">
@@ -5407,6 +7882,17 @@
           <t>非洲市場情報與分析</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n">
@@ -5432,6 +7918,17 @@
           <t>澳洲 Skill-based EGM 專題研究報告（單一 PDF，非持續更新頁面）</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="13" t="inlineStr"/>
@@ -5460,6 +7957,21 @@
           <t>美國博彩設備商協會（AGEM）產業指數</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://www.agem.org/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="n">
@@ -5485,6 +7997,21 @@
           <t>AGEM 新聞版</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://www.agem.org/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n">
@@ -5510,6 +8037,21 @@
           <t>Gaming Laboratories International 技術標準；子頁 /igaming/igaming-technical-standards/ 與中文版為 iGaming 專屬技術標準</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://gaminglabs.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="n">
@@ -5535,6 +8077,21 @@
           <t>博彩通訊協定國際標準組織</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://igsa.org/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="n">
@@ -5560,6 +8117,17 @@
           <t>第三方遊戲測試／認證機構</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n">
@@ -5585,6 +8153,21 @@
           <t>美國博彩協會（AGA）研究部門</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://www.americangaming.org/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="3" t="n">
@@ -5610,6 +8193,21 @@
           <t>AGA 年度旗艦市場報告</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://www.americangaming.org/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="n">
@@ -5635,6 +8233,21 @@
           <t>西班牙數位博彩產業協會</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://www.jdigital.es/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="n">
@@ -5660,6 +8273,21 @@
           <t>西班牙遊藝廳／自動機協會</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://www.anesar.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="n">
@@ -5685,6 +8313,21 @@
           <t>西班牙博彩業聯合會</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://cejuego.com/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="3" t="n">
@@ -5710,6 +8353,21 @@
           <t>西班牙機台供應鏈俱樂部</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://clubdeconvergentes.es/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="n">
@@ -5735,6 +8393,21 @@
           <t>義大利娛樂機台協會；子頁 /apparecchi-intrattenimento 為設備分類頁</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://www.jamma.it/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="3" t="n">
@@ -5760,6 +8433,17 @@
           <t>義大利博彩產業協會</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="n">
@@ -5785,6 +8469,21 @@
           <t>德國機台產業協會</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://www.automatenwirtschaft.de/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="3" t="n">
@@ -5810,6 +8509,17 @@
           <t>德國機台製造商協會</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="n">
@@ -5835,6 +8545,21 @@
           <t>法國賭場協會</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://casinos.fr/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="3" t="n">
@@ -5860,6 +8585,21 @@
           <t>日本 Pachislot 廠商協同組合</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://www.nichidenkyo.or.jp/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="n">
@@ -5885,6 +8625,21 @@
           <t>日本遊技機製造商工業組合</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://nikkoso.jp/feed/</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="3" t="n">
@@ -5910,6 +8665,17 @@
           <t>韓國賭場協會</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="n">
@@ -5935,6 +8701,21 @@
           <t>澳洲機台製造商協會</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://www.gamingta.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="3" t="n">
@@ -5960,6 +8741,17 @@
           <t>澳洲博彩產業研究協會</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="n">
@@ -5985,6 +8777,17 @@
           <t>墨西哥博彩產業協會</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>每週／事件</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="n">
@@ -6010,6 +8813,21 @@
           <t>拉丁美洲暨伊比利半島博彩監理機關聯盟（監理機關組成的跨國協會）</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://cibelae.net/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="14" t="inlineStr"/>
@@ -6038,6 +8856,17 @@
           <t>網站已停止營運（2026-06-15 確認），不再抓取</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>不抓</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="n">
@@ -6063,6 +8892,17 @@
           <t>舊網域已出售停站（2026-06-15 確認）；★本次比對發現公司已搬遷新網域 ekgamingllc.com，新網域資料已收錄於「市場數據／分析公司」分類，建議日後改用新網域</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>不抓</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -6088,6 +8928,17 @@
           <t>★優先追蹤｜IGS鈊象電子旗下 GP；可視為 Jili 低配版、多款與 Jili 互通，B 端價格有優勢。上新遊戲於 DigiPlus 系(BingoPlus/ArenaPlus/GameZone)或 CasinoPlus 等菲現金網、或特別線上/線下活動與平台功能更新→提高露出權重</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -6113,6 +8964,17 @@
           <t>★優先追蹤｜台灣尊博集團 GP；Super Gem 對標 Fortune Gem 成功、獲 BingoPlus/CasinoPlus 內部認可、菲律賓有成績。上新遊戲於 DigiPlus 系/CasinoPlus 或特別活動/平台更新→提高露出權重</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>輪掃</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -6138,6 +9000,21 @@
           <t>★優先追蹤｜菲律賓平台 PlayTime 深度策略夥伴。上新遊戲於 DigiPlus 系/CasinoPlus/PlayTime 或特別活動/平台更新→提高露出權重</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://www.yellowbat.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -6161,6 +9038,341 @@
       <c r="E234" t="inlineStr">
         <is>
           <t>iGaming/Slot 新聞媒體，新老虎機上線與供應商動態報導快、覆蓋廣；交叉查證 Slot 新遊戲的重點來源之一</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://slotbeats.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>224</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>產業媒體</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>GMA News</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>https://www.gmanetwork.com/news/</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>菲律賓在地媒體（v6.4 新增）；全站 RSS，需用博弈關鍵字過濾</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://www.gmanetwork.com/rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>225</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>產業媒體</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Rappler</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>https://www.rappler.com/</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>菲律賓在地媒體（v6.4 新增）；WP API，需用博弈關鍵字過濾</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>WP-API</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://www.rappler.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>226</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>產業媒體</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SunStar</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>https://www.sunstar.com.ph/</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>菲律賓在地媒體（v6.4 新增）；需用博弈關鍵字過濾</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://www.sunstar.com.ph/feed/</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>227</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>產業媒體</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>BusinessWorld</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>https://www.bworldonline.com/</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>菲律賓財經媒體（v6.4 新增）；DigiPlus／Bloomberry 等上市公司動態</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://bworldonline.com/feed/</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>228</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>產業媒體</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>DigiPlus</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>https://digiplus.com.ph/news/</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>★DigiPlus 官網新聞（v6.4 新增）；BingoPlus／ArenaPlus／GameZone 主來源</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://digiplus.com.ph/feed/</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>229</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>產品分析／評測</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>BigWinBoard</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>https://www.bigwinboard.com/new-slots/</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Slot 資料庫站（v6.4 新增）；新作依上線日排序，大廠幾乎都有，含 RTP／最高倍率</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://www.bigwinboard.com/new-slots/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>230</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>產品分析／評測</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SlotsLaunch</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>https://slotslaunch.com/</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Slot 資料庫站（v6.4 新增）；新作與上線日</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://slotslaunch.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>231</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>產業媒體</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>EEGaming（Recent Slot Releases）</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>https://eegaming.org/category/recent-slot-releases</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Slot 新作通稿集中地（v6.4 新增）；每週五另有 Weekend Reels 整理</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://eegaming.org/category/recent-slot-releases</t>
         </is>
       </c>
     </row>

--- a/sources/igaming-daily-report-sources-v2.xlsx
+++ b/sources/igaming-daily-report-sources-v2.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:J244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -573,6 +573,16 @@
           <t>抓取端點</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>觸發關鍵字</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>展期</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr"/>
@@ -651,7 +661,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -687,7 +696,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -763,7 +771,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -799,7 +806,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -835,7 +841,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -871,7 +876,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -907,7 +911,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -943,7 +946,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -979,7 +981,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1055,7 +1056,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1091,7 +1091,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1207,7 +1206,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1243,7 +1241,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1279,7 +1276,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1435,7 +1431,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1471,7 +1466,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr"/>
@@ -1550,7 +1544,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -1586,7 +1579,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -1622,7 +1614,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -1658,7 +1649,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -1694,7 +1684,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -1730,7 +1719,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -1886,7 +1874,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr"/>
@@ -2285,7 +2272,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -2321,7 +2307,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -2397,7 +2382,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -2433,7 +2417,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -2669,7 +2652,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -2705,7 +2687,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -2741,7 +2722,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -2777,7 +2757,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -2853,7 +2832,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -3249,7 +3227,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
@@ -3285,7 +3262,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
@@ -3441,7 +3417,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
@@ -3477,7 +3452,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
@@ -3513,7 +3487,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
@@ -3629,7 +3602,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
@@ -3745,7 +3717,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
@@ -3981,7 +3952,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
@@ -4377,7 +4347,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
@@ -4453,7 +4422,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
@@ -4489,7 +4457,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
@@ -4525,7 +4492,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
@@ -4601,7 +4567,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
@@ -4717,7 +4682,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
@@ -4753,7 +4717,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
@@ -4789,7 +4752,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
@@ -4865,7 +4827,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
@@ -4901,7 +4862,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
@@ -4937,7 +4897,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
@@ -4973,7 +4932,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
@@ -5209,7 +5167,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
@@ -5245,7 +5202,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
@@ -5361,7 +5317,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
@@ -5600,7 +5555,6 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
@@ -5636,7 +5590,6 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
@@ -5672,7 +5625,6 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
@@ -5708,7 +5660,6 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
@@ -5744,7 +5695,6 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
@@ -5780,7 +5730,6 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="9" t="inlineStr"/>
@@ -5816,10 +5765,14 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>2027-01-18~2027-01-20</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
@@ -5852,10 +5805,14 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2026-11-02~2026-11-05;2027-05-03~2027-05-05</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
@@ -5873,12 +5830,12 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>https://www.reiexpo.com/g2e</t>
+          <t>https://www.globalgamingexpo.com/</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>每年秋季，北美最大；⚠️官方新網域為 globalgamingexpo.com，建議之後更新</t>
+          <t>每年秋季，北美最大實體機台與 iGaming 展（官方網域 globalgamingexpo.com）</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5888,10 +5845,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2026-09-28~2026-10-01;2027-09-27~2027-09-30</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
@@ -5924,10 +5885,14 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2027-03-15~2027-03-17</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
@@ -5960,10 +5925,14 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>2027-03-15~2027-03-17</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
@@ -5991,12 +5960,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>RSS</t>
+          <t>Firecrawl</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>每日</t>
+          <t>行事曆</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6036,10 +6005,9 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
@@ -6072,10 +6040,14 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2027-01-18~2027-01-20</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
@@ -6108,10 +6080,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2027-01-18~2027-01-20</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
@@ -6144,10 +6120,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2027-05-18~2027-05-20</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
@@ -6180,10 +6160,14 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2027-05-31~2027-06-03</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
@@ -6211,17 +6195,22 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>WP-API</t>
+          <t>Firecrawl</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>每日</t>
+          <t>行事曆</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
           <t>https://gatexpo.net/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2026-10-15~2026-10-15;2026-11-18~2026-11-18;2027-03-30~2027-04-01;2027-06-02~2027-06-03;2027-07-01~2027-07-02;2027-10-21~2027-10-21</t>
         </is>
       </c>
     </row>
@@ -6251,17 +6240,22 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>WP-API</t>
+          <t>Firecrawl</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>每日</t>
+          <t>行事曆</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
           <t>https://www.perugamingshow.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>2027-06-16~2027-06-17</t>
         </is>
       </c>
     </row>
@@ -6296,10 +6290,14 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>2027-03-17~2027-03-18;2027-08-04~2027-08-06</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
@@ -6327,17 +6325,22 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>WP-API</t>
+          <t>Firecrawl</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>每日</t>
+          <t>行事曆</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
           <t>https://austgamingexpo.com/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>2027-08-10~2027-08-12</t>
         </is>
       </c>
     </row>
@@ -6372,10 +6375,14 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2027-05-04~2027-05-06</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
@@ -6403,17 +6410,22 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>WP-API</t>
+          <t>Firecrawl</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>每日</t>
+          <t>行事曆</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
           <t>https://www.ageafrique.org/wp-json/wp/v2/posts</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>2027-03-16~2027-03-19</t>
         </is>
       </c>
     </row>
@@ -6448,10 +6460,14 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2027-02-15~2027-02-17</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
@@ -6484,10 +6500,14 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>每週／事件</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr"/>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>2027-04-05~2027-04-08</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="10" t="inlineStr"/>
@@ -6526,7 +6546,6 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
@@ -6562,7 +6581,6 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
@@ -6638,7 +6656,6 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
@@ -6674,7 +6691,6 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr"/>
@@ -6713,7 +6729,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>DGOJ|Ordenación del Juego</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
@@ -6749,7 +6769,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Agenzia delle Dogane|\bADM\b</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
@@ -6865,7 +6889,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Belgian Gaming Commission|Kansspelcommissie</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
@@ -6901,7 +6929,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>ESBK|Swiss Federal Gaming Board</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
@@ -6937,7 +6969,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>DICJ|Gaming Inspection and Coordination</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
@@ -6973,7 +7009,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>PAGCOR</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
@@ -7009,7 +7049,6 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n">
@@ -7045,7 +7084,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Coljuegos</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
@@ -7081,7 +7124,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>MINCETUR</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n">
@@ -7117,7 +7164,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>NSW gaming research</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n">
@@ -7153,7 +7204,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Liquor (&amp;|and) Gaming NSW</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n">
@@ -7189,7 +7244,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>VGCCC|Victorian Gambling and Casino Control</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="n">
@@ -7225,7 +7284,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>\bOLGR\b|Office of Liquor and Gaming</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n">
@@ -7261,7 +7324,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Department of Internal Affairs|New Zealand DIA</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="12" t="inlineStr"/>
@@ -7300,7 +7367,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n">
@@ -7336,7 +7402,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="n">
@@ -7372,7 +7437,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="n">
@@ -7448,7 +7512,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n">
@@ -7484,7 +7547,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n">
@@ -7520,7 +7582,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n">
@@ -7556,7 +7617,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n">
@@ -7592,7 +7652,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n">
@@ -7628,7 +7687,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n">
@@ -7664,7 +7722,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n">
@@ -7780,7 +7837,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n">
@@ -7816,7 +7872,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n">
@@ -7892,7 +7947,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n">
@@ -7928,7 +7982,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="13" t="inlineStr"/>
@@ -8127,7 +8180,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>BMM Testlabs</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n">
@@ -8443,7 +8500,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Sistema Gioco Italia</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="3" t="n">
@@ -8519,7 +8580,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>\bVDAI\b</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="3" t="n">
@@ -8675,7 +8740,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Korea Casino Association</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="3" t="n">
@@ -8751,7 +8820,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Australasian Gaming Council</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="n">
@@ -8787,7 +8860,11 @@
           <t>每週／事件</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>AIEJA</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="3" t="n">
@@ -8866,7 +8943,6 @@
           <t>停用</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="n">
@@ -8902,7 +8978,6 @@
           <t>停用</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -8938,7 +9013,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -8974,7 +9048,6 @@
           <t>輪掃</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -9373,6 +9446,90 @@
       <c r="H242" t="inlineStr">
         <is>
           <t>https://eegaming.org/category/recent-slot-releases</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>232</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>展會</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SBC Summit</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>https://sbcevents.com/sbc-summit/</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>里斯本，歐洲最大 iGaming／博彩 B2B 展之一（v6.4.2 新增）</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>2026-09-29~2026-10-01;2027-09-21~2027-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>233</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>展會</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>iGB Live</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>https://www.igblive.com/</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>倫敦，iGaming Business 主辦（v6.4.2 新增）</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Firecrawl</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>行事曆</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>2027-07-07~2027-07-08</t>
         </is>
       </c>
     </row>

--- a/sources/igaming-daily-report-sources-v2.xlsx
+++ b/sources/igaming-daily-report-sources-v2.xlsx
@@ -2019,12 +2019,12 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>盤口動態、Provider 合作</t>
+          <t>盤口動態、Provider 合作；v6.5 改用 RSS（10 則約 3 天，免費）</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Firecrawl</t>
+          <t>RSS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://sbcnews.co.uk/</t>
+          <t>https://sbcnews.co.uk/feed/</t>
         </is>
       </c>
     </row>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>亞洲供應商、機台、展會報導</t>
+          <t>亞洲供應商、機台、展會報導；v6.5 改用 RSS（10 則約 3 天，免費）</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Firecrawl</t>
+          <t>RSS</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.asgam.com/</t>
+          <t>https://asgam.com/feed/</t>
         </is>
       </c>
     </row>
@@ -9355,7 +9355,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Firecrawl</t>
+          <t>程式解析</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Slot 資料庫站（v6.4 新增）；新作與上線日</t>
+          <t>Slot 資料庫站（v6.4 新增）；v6.5 改抓上線日曆（每款有上線日，免費）</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Firecrawl</t>
+          <t>程式解析</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>https://slotslaunch.com/</t>
+          <t>https://slotslaunch.com/calendar</t>
         </is>
       </c>
     </row>
@@ -9430,12 +9430,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Slot 新作通稿集中地（v6.4 新增）；每週五另有 Weekend Reels 整理</t>
+          <t>Slot 新作通稿集中地（v6.4 新增）；每週五另有 Weekend Reels 整理；v6.5 改用全站 RSS（精確發布時間、免費）</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Firecrawl</t>
+          <t>RSS</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>https://eegaming.org/category/recent-slot-releases</t>
+          <t>https://eegaming.org/feed</t>
         </is>
       </c>
     </row>
@@ -9483,8 +9483,6 @@
           <t>行事曆</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
           <t>2026-09-29~2026-10-01;2027-09-21~2027-09-23</t>
@@ -9525,8 +9523,6 @@
           <t>行事曆</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
           <t>2027-07-07~2027-07-08</t>

--- a/sources/igaming-daily-report-sources-v2.xlsx
+++ b/sources/igaming-daily-report-sources-v2.xlsx
@@ -718,12 +718,12 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Provider 官網</t>
+          <t>Provider 官網；v6.5.2 官網改 Wix、RSS 消失 → 改抓 sitemap（/games/ 的日期＝上線日，/post/ 為新聞）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RSS</t>
+          <t>Sitemap</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.playngo.com/blog-feed.xml</t>
+          <t>https://www.playngo.com/sitemap.xml</t>
         </is>
       </c>
     </row>
@@ -1378,22 +1378,22 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Provider 官網</t>
+          <t>Provider 官網；v6.5.2 網站加了機器人驗證（curl 被擋）→ 改 Firecrawl 輪掃</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WP-API</t>
+          <t>Firecrawl</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>每日</t>
+          <t>輪掃</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://kalambagames.com/wp-json/wp/v2/posts</t>
+          <t>https://kalambagames.com/</t>
         </is>
       </c>
     </row>
@@ -4514,22 +4514,22 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>羅馬尼亞博彩媒體</t>
+          <t>羅馬尼亞博彩媒體；v6.5.2 網站加了機器人驗證（curl 被擋）→ 改 Firecrawl 輪掃</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>WP-API</t>
+          <t>Firecrawl</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>每日</t>
+          <t>輪掃</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://casinoinside.ro/wp-json/wp/v2/posts</t>
+          <t>https://casinoinside.ro/</t>
         </is>
       </c>
     </row>

--- a/sources/igaming-daily-report-sources-v2.xlsx
+++ b/sources/igaming-daily-report-sources-v2.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J244"/>
+  <dimension ref="A1:J251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9526,6 +9526,286 @@
       <c r="J244" t="inlineStr">
         <is>
           <t>2027-07-07~2027-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>234</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>產業媒體</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Google News：BingoPlus</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>https://news.google.com/</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>v6.6.9 菲律賓平台品牌的在地媒體報導（BusinessMirror、Manila Times、Inquirer…）；連結由程式轉回原文；一律歸 cat4</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>GoogleNews</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22BingoPlus%22%20when%3A3d&amp;hl=en-PH&amp;gl=PH&amp;ceid=PH:en</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>235</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>產業媒體</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Google News：ArenaPlus</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>https://news.google.com/</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>v6.6.9 菲律賓平台品牌的在地媒體報導（BusinessMirror、Manila Times、Inquirer…）；連結由程式轉回原文；一律歸 cat4</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>GoogleNews</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22ArenaPlus%22%20when%3A3d&amp;hl=en-PH&amp;gl=PH&amp;ceid=PH:en</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>236</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>產業媒體</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Google News：GameZone</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>https://news.google.com/</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>v6.6.9 菲律賓平台品牌的在地媒體報導（BusinessMirror、Manila Times、Inquirer…）；連結由程式轉回原文；一律歸 cat4</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>GoogleNews</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22GameZone%22%20%28DigiPlus%20OR%20Philippines%20OR%20tongits%20OR%20PAGCOR%20OR%20GZone%29%20when%3A3d&amp;hl=en-PH&amp;gl=PH&amp;ceid=PH:en</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>237</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>產業媒體</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Google News：Casino Plus</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>https://news.google.com/</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>v6.6.9 菲律賓平台品牌的在地媒體報導（BusinessMirror、Manila Times、Inquirer…）；連結由程式轉回原文；一律歸 cat4</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>GoogleNews</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22Casino%20Plus%22%20Philippines%20when%3A3d&amp;hl=en-PH&amp;gl=PH&amp;ceid=PH:en</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>238</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>產業媒體</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Google News：PlayTime／PT Gaming</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>https://news.google.com/</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>v6.6.9 菲律賓平台品牌的在地媒體報導（BusinessMirror、Manila Times、Inquirer…）；連結由程式轉回原文；一律歸 cat4</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>GoogleNews</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%28%22PlayTime%20Entertainment%22%20OR%20%22PT%20Gaming%22%20OR%20%22PlayTime%22%20PAGCOR%20OR%20%22PlayTime%22%20sponsorship%20OR%20%22PlayTime%22%20NCAA%29%20when%3A3d&amp;hl=en-PH&amp;gl=PH&amp;ceid=PH:en</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>239</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>產業媒體</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Google News：OKBet</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>https://news.google.com/</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>v6.6.9 菲律賓平台品牌的在地媒體報導（BusinessMirror、Manila Times、Inquirer…）；連結由程式轉回原文；一律歸 cat4</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>GoogleNews</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22OKBet%22%20when%3A3d&amp;hl=en-PH&amp;gl=PH&amp;ceid=PH:en</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>240</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>產業媒體</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Google News：BET88</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>https://news.google.com/</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>v6.6.9 菲律賓平台品牌的在地媒體報導（BusinessMirror、Manila Times、Inquirer…）；連結由程式轉回原文；一律歸 cat4</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>GoogleNews</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>每日</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/search?q=%22BET88%22%20when%3A3d&amp;hl=en-PH&amp;gl=PH&amp;ceid=PH:en</t>
         </is>
       </c>
     </row>
